--- a/Source/Data/UALAllOperations.xlsx
+++ b/Source/Data/UALAllOperations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2365" uniqueCount="2365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2368" uniqueCount="2368">
   <si>
     <t>Risk</t>
   </si>
@@ -7115,6 +7115,15 @@
   </si>
   <si>
     <t>Set-MailboxCalendarConfiguration</t>
+  </si>
+  <si>
+    <t>Consent to application.</t>
+  </si>
+  <si>
+    <t>Remove delegated permission grant.</t>
+  </si>
+  <si>
+    <t>Add delegated permission grant.</t>
   </si>
 </sst>
 </file>
@@ -7881,8 +7890,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}" name="Table1" displayName="Table1" ref="A1:G841" totalsRowShown="0">
-  <autoFilter ref="A1:G835" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}" name="Table1" displayName="Table1" ref="A1:G847" totalsRowShown="0">
+  <autoFilter ref="A1:G844" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G835">
     <sortCondition ref="D2:D835"/>
   </sortState>
@@ -8216,7 +8225,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{207B3246-3E1F-4883-B5B7-F0312ED8EA41}">
-  <dimension ref="A1:G841"/>
+  <dimension ref="A1:G847"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="8.140625" customWidth="1"/>
@@ -17963,6 +17972,72 @@
       </c>
       <c r="D841" s="0" t="s">
         <v>2364</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="B842" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C842" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D842" s="0" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="B843" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C843" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D843" s="0" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="B844" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C844" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D844" s="0" t="s">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="B845" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C845" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D845" s="0" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="B846" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C846" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D846" s="0" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="B847" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C847" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D847" s="0" t="s">
+        <v>2367</v>
       </c>
     </row>
   </sheetData>

--- a/Source/Data/UALAllOperations.xlsx
+++ b/Source/Data/UALAllOperations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2368" uniqueCount="2368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2369" uniqueCount="2369">
   <si>
     <t>Risk</t>
   </si>
@@ -7124,6 +7124,9 @@
   </si>
   <si>
     <t>Add delegated permission grant.</t>
+  </si>
+  <si>
+    <t>CallParticipantDetail</t>
   </si>
 </sst>
 </file>
@@ -7890,8 +7893,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}" name="Table1" displayName="Table1" ref="A1:G847" totalsRowShown="0">
-  <autoFilter ref="A1:G844" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}" name="Table1" displayName="Table1" ref="A1:G848" totalsRowShown="0">
+  <autoFilter ref="A1:G847" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G835">
     <sortCondition ref="D2:D835"/>
   </sortState>
@@ -8225,7 +8228,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{207B3246-3E1F-4883-B5B7-F0312ED8EA41}">
-  <dimension ref="A1:G847"/>
+  <dimension ref="A1:G848"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="8.140625" customWidth="1"/>
@@ -18038,6 +18041,17 @@
       </c>
       <c r="D847" s="0" t="s">
         <v>2367</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="B848" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C848" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D848" s="0" t="s">
+        <v>2368</v>
       </c>
     </row>
   </sheetData>

--- a/Source/Data/UALAllOperations.xlsx
+++ b/Source/Data/UALAllOperations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2369" uniqueCount="2369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2375" uniqueCount="2375">
   <si>
     <t>Risk</t>
   </si>
@@ -7127,6 +7127,24 @@
   </si>
   <si>
     <t>CallParticipantDetail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Update application – Certificates and secrets management </t>
+  </si>
+  <si>
+    <t>Update service principal.</t>
+  </si>
+  <si>
+    <t>Update application.</t>
+  </si>
+  <si>
+    <t>Add app role assignment to service principal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create application – Certificates and secrets management </t>
+  </si>
+  <si>
+    <t>Delete application.</t>
   </si>
 </sst>
 </file>
@@ -7893,8 +7911,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}" name="Table1" displayName="Table1" ref="A1:G848" totalsRowShown="0">
-  <autoFilter ref="A1:G847" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}" name="Table1" displayName="Table1" ref="A1:G855" totalsRowShown="0">
+  <autoFilter ref="A1:G848" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G835">
     <sortCondition ref="D2:D835"/>
   </sortState>
@@ -8228,7 +8246,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{207B3246-3E1F-4883-B5B7-F0312ED8EA41}">
-  <dimension ref="A1:G848"/>
+  <dimension ref="A1:G855"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="8.140625" customWidth="1"/>
@@ -18052,6 +18070,83 @@
       </c>
       <c r="D848" s="0" t="s">
         <v>2368</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="B849" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C849" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D849" s="0" t="s">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="B850" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C850" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D850" s="0" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="B851" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C851" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D851" s="0" t="s">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="B852" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C852" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D852" s="0" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="B853" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C853" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D853" s="0" t="s">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="B854" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C854" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D854" s="0" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="B855" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C855" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D855" s="0" t="s">
+        <v>2374</v>
       </c>
     </row>
   </sheetData>

--- a/Source/Data/UALAllOperations.xlsx
+++ b/Source/Data/UALAllOperations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2375" uniqueCount="2375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2376" uniqueCount="2376">
   <si>
     <t>Risk</t>
   </si>
@@ -7145,6 +7145,9 @@
   </si>
   <si>
     <t>Delete application.</t>
+  </si>
+  <si>
+    <t>Remove-StoreMailbox</t>
   </si>
 </sst>
 </file>
@@ -7911,8 +7914,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}" name="Table1" displayName="Table1" ref="A1:G855" totalsRowShown="0">
-  <autoFilter ref="A1:G848" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}" name="Table1" displayName="Table1" ref="A1:G856" totalsRowShown="0">
+  <autoFilter ref="A1:G855" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G835">
     <sortCondition ref="D2:D835"/>
   </sortState>
@@ -8246,7 +8249,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{207B3246-3E1F-4883-B5B7-F0312ED8EA41}">
-  <dimension ref="A1:G855"/>
+  <dimension ref="A1:G856"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="8.140625" customWidth="1"/>
@@ -18147,6 +18150,17 @@
       </c>
       <c r="D855" s="0" t="s">
         <v>2374</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="B856" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="C856" s="0" t="s">
+        <v>594</v>
+      </c>
+      <c r="D856" s="0" t="s">
+        <v>2375</v>
       </c>
     </row>
   </sheetData>

--- a/Source/Data/UALAllOperations.xlsx
+++ b/Source/Data/UALAllOperations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2376" uniqueCount="2376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2387" uniqueCount="2387">
   <si>
     <t>Risk</t>
   </si>
@@ -7148,6 +7148,39 @@
   </si>
   <si>
     <t>Remove-StoreMailbox</t>
+  </si>
+  <si>
+    <t>ModifyFolderPermissions</t>
+  </si>
+  <si>
+    <t>MessageReadReceiptReceived</t>
+  </si>
+  <si>
+    <t>FileVersionsAllDeleted</t>
+  </si>
+  <si>
+    <t>FeatureActivated</t>
+  </si>
+  <si>
+    <t>SPOTenantCmdlets</t>
+  </si>
+  <si>
+    <t>MicrosoftTodo</t>
+  </si>
+  <si>
+    <t>MicrosoftTodoAudit</t>
+  </si>
+  <si>
+    <t>Copilot</t>
+  </si>
+  <si>
+    <t>Remove app role assignment from user.</t>
+  </si>
+  <si>
+    <t>Add policy to service principal.</t>
+  </si>
+  <si>
+    <t>Add device.</t>
   </si>
 </sst>
 </file>
@@ -7914,8 +7947,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}" name="Table1" displayName="Table1" ref="A1:G856" totalsRowShown="0">
-  <autoFilter ref="A1:G855" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}" name="Table1" displayName="Table1" ref="A1:G886" totalsRowShown="0">
+  <autoFilter ref="A1:G883" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G835">
     <sortCondition ref="D2:D835"/>
   </sortState>
@@ -8249,7 +8282,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{207B3246-3E1F-4883-B5B7-F0312ED8EA41}">
-  <dimension ref="A1:G856"/>
+  <dimension ref="A1:G886"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="8.140625" customWidth="1"/>
@@ -18161,6 +18194,336 @@
       </c>
       <c r="D856" s="0" t="s">
         <v>2375</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="B857" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C857" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D857" s="0" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="B858" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C858" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D858" s="0" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="B859" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="C859" s="0" t="s">
+        <v>456</v>
+      </c>
+      <c r="D859" s="0" t="s">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="B860" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C860" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="D860" s="0" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="B861" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C861" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D861" s="0" t="s">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="B862" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="C862" s="0" t="s">
+        <v>737</v>
+      </c>
+      <c r="D862" s="0" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="B863" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="C863" s="0" t="s">
+        <v>737</v>
+      </c>
+      <c r="D863" s="0" t="s">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="B864" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C864" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="D864" s="0" t="s">
+        <v>2379</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="B865" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C865" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="D865" s="0" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="B866" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C866" s="0" t="s">
+        <v>737</v>
+      </c>
+      <c r="D866" s="0" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="B867" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C867" s="0" t="s">
+        <v>737</v>
+      </c>
+      <c r="D867" s="0" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="B868" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C868" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="D868" s="0" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="B869" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C869" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="D869" s="0" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="B870" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C870" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="D870" s="0" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="B871" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C871" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="D871" s="0" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="B872" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C872" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="D872" s="0" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="B873" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C873" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="D873" s="0" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="B874" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C874" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="D874" s="0" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="B875" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C875" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D875" s="0" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="B876" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C876" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="D876" s="0" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="B877" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="C877" s="0" t="s">
+        <v>961</v>
+      </c>
+      <c r="D877" s="0" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="B878" s="0" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C878" s="0" t="s">
+        <v>2382</v>
+      </c>
+      <c r="D878" s="0" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="B879" s="0" t="s">
+        <v>2383</v>
+      </c>
+      <c r="C879" s="0" t="s">
+        <v>450</v>
+      </c>
+      <c r="D879" s="0" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="B880" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C880" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D880" s="0" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="B881" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C881" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D881" s="0" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="B882" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C882" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D882" s="0" t="s">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="B883" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C883" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D883" s="0" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="B884" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C884" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D884" s="0" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="B885" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="C885" s="0" t="s">
+        <v>737</v>
+      </c>
+      <c r="D885" s="0" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="B886" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="C886" s="0" t="s">
+        <v>737</v>
+      </c>
+      <c r="D886" s="0" t="s">
+        <v>774</v>
       </c>
     </row>
   </sheetData>

--- a/Source/Data/UALAllOperations.xlsx
+++ b/Source/Data/UALAllOperations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2387" uniqueCount="2387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2405" uniqueCount="2405">
   <si>
     <t>Risk</t>
   </si>
@@ -7181,6 +7181,60 @@
   </si>
   <si>
     <t>Add device.</t>
+  </si>
+  <si>
+    <t>DataInsightsRestApiAudit</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
+    <t>SecurityComplianceCenterEOPCmdlet</t>
+  </si>
+  <si>
+    <t>Get-Label</t>
+  </si>
+  <si>
+    <t>Get-AutoSensitivityLabelPolicy</t>
+  </si>
+  <si>
+    <t>Get-LabelPolicy</t>
+  </si>
+  <si>
+    <t>Get-DlpSensitiveInformationType</t>
+  </si>
+  <si>
+    <t>Mip</t>
+  </si>
+  <si>
+    <t>MipLabelAnalyticsAuditRecord</t>
+  </si>
+  <si>
+    <t>AccessedAggregates</t>
+  </si>
+  <si>
+    <t>Validate</t>
+  </si>
+  <si>
+    <t>PowerPlatform</t>
+  </si>
+  <si>
+    <t>PowerPlatformAdministratorActivity</t>
+  </si>
+  <si>
+    <t>ApiEndpointCallEvent</t>
+  </si>
+  <si>
+    <t>ReactedToMessage</t>
+  </si>
+  <si>
+    <t>SharingLinkUpdated</t>
+  </si>
+  <si>
+    <t>SharingLinkCreated</t>
+  </si>
+  <si>
+    <t>FileAccessedExtended</t>
   </si>
 </sst>
 </file>
@@ -7947,8 +8001,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}" name="Table1" displayName="Table1" ref="A1:G886" totalsRowShown="0">
-  <autoFilter ref="A1:G883" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}" name="Table1" displayName="Table1" ref="A1:G906" totalsRowShown="0">
+  <autoFilter ref="A1:G898" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G835">
     <sortCondition ref="D2:D835"/>
   </sortState>
@@ -8282,7 +8336,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{207B3246-3E1F-4883-B5B7-F0312ED8EA41}">
-  <dimension ref="A1:G886"/>
+  <dimension ref="A1:G906"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="8.140625" customWidth="1"/>
@@ -18524,6 +18578,226 @@
       </c>
       <c r="D886" s="0" t="s">
         <v>774</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="B887" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C887" s="0" t="s">
+        <v>2387</v>
+      </c>
+      <c r="D887" s="0" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="B888" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C888" s="0" t="s">
+        <v>2389</v>
+      </c>
+      <c r="D888" s="0" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="B889" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C889" s="0" t="s">
+        <v>2389</v>
+      </c>
+      <c r="D889" s="0" t="s">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="B890" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C890" s="0" t="s">
+        <v>2389</v>
+      </c>
+      <c r="D890" s="0" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="B891" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C891" s="0" t="s">
+        <v>2389</v>
+      </c>
+      <c r="D891" s="0" t="s">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="B892" s="0" t="s">
+        <v>2394</v>
+      </c>
+      <c r="C892" s="0" t="s">
+        <v>2395</v>
+      </c>
+      <c r="D892" s="0" t="s">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="B893" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C893" s="0" t="s">
+        <v>2387</v>
+      </c>
+      <c r="D893" s="0" t="s">
+        <v>2397</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="B894" s="0" t="s">
+        <v>2398</v>
+      </c>
+      <c r="C894" s="0" t="s">
+        <v>2399</v>
+      </c>
+      <c r="D894" s="0" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="B895" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="C895" s="0" t="s">
+        <v>456</v>
+      </c>
+      <c r="D895" s="0" t="s">
+        <v>2256</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="B896" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C896" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D896" s="0" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="B897" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C897" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D897" s="0" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="B898" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C898" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D898" s="0" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="B899" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C899" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D899" s="0" t="s">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="B900" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C900" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="D900" s="0" t="s">
+        <v>2402</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="B901" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C901" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="D901" s="0" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="B902" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C902" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="D902" s="0" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="B903" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C903" s="0" t="s">
+        <v>737</v>
+      </c>
+      <c r="D903" s="0" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="B904" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C904" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="D904" s="0" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="B905" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C905" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="D905" s="0" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="B906" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="C906" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="D906" s="0" t="s">
+        <v>1729</v>
       </c>
     </row>
   </sheetData>

--- a/Source/Data/UALAllOperations.xlsx
+++ b/Source/Data/UALAllOperations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://syseng0365-my.sharepoint.com/personal/ezappe_syseng_com/Documents/Documents/Powershell_Modules/M365IncidentResponseTools/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ezappe\dev\powershell\M365IncidentResponseTools\Source\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{88BDCCE0-A36D-47CD-BC42-65B70A78859F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C14E72E9-3610-4487-B933-02D57173909C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5534710-453D-4E3C-A332-9E86CEADBB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60735" yWindow="5160" windowWidth="33135" windowHeight="25095" xr2:uid="{A03DE0A1-0BA6-45A9-BE83-66EA3AAEEDA8}"/>
+    <workbookView xWindow="2295" yWindow="2295" windowWidth="28635" windowHeight="25455" xr2:uid="{A03DE0A1-0BA6-45A9-BE83-66EA3AAEEDA8}"/>
   </bookViews>
   <sheets>
     <sheet name="Operations" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2405" uniqueCount="2405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2417" uniqueCount="2417">
   <si>
     <t>Risk</t>
   </si>
@@ -6460,9 +6460,6 @@
     <t>TIMailData</t>
   </si>
   <si>
-    <t>Threat Intel Mail Event</t>
-  </si>
-  <si>
     <t>Microsoft Threat Intel registers an event related to email. I've seen this event trigger when a phishing email is detected.</t>
   </si>
   <si>
@@ -7235,6 +7232,45 @@
   </si>
   <si>
     <t>FileAccessedExtended</t>
+  </si>
+  <si>
+    <t>ThreatIntelligenceUrl</t>
+  </si>
+  <si>
+    <t>TIUrlClickData</t>
+  </si>
+  <si>
+    <t>Ocurrs when the user clicks a link in a known phishing email.</t>
+  </si>
+  <si>
+    <t>Compliance</t>
+  </si>
+  <si>
+    <t>AeD</t>
+  </si>
+  <si>
+    <t>PublicEndpoint</t>
+  </si>
+  <si>
+    <t>OfficeRestrictedModeAction</t>
+  </si>
+  <si>
+    <t>HKCUAddinBlocked</t>
+  </si>
+  <si>
+    <t>XLMBlocked</t>
+  </si>
+  <si>
+    <t>Set-MailboxAutoReplyConfiguration</t>
+  </si>
+  <si>
+    <t>ComplianceSupervisionExchange</t>
+  </si>
+  <si>
+    <t>FolderBind</t>
+  </si>
+  <si>
+    <t>Update device.</t>
   </si>
 </sst>
 </file>
@@ -7807,183 +7843,7 @@
     <cellStyle name="Total" xfId="40" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="41" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="25">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB6C1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB6C1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB6C1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFAFAD2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB6C1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB6C1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFAFAD2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFAFAD2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB6C1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFAFAD2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFAFAD2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFAFAD2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB6C1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB6C1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB6C1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFAFAD2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFAFAD2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFAFAD2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFAFAD2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFAFAD2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFAFAD2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB6C1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB6C1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB6C1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFB6C1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -7996,13 +7856,9 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}" name="Table1" displayName="Table1" ref="A1:G906" totalsRowShown="0">
-  <autoFilter ref="A1:G898" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}" name="Table1" displayName="Table1" ref="A1:G933" totalsRowShown="0">
+  <autoFilter ref="A1:G931" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G835">
     <sortCondition ref="D2:D835"/>
   </sortState>
@@ -8336,7 +8192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{207B3246-3E1F-4883-B5B7-F0312ED8EA41}">
-  <dimension ref="A1:G906"/>
+  <dimension ref="A1:G933"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="8.140625" customWidth="1"/>
@@ -17091,198 +16947,195 @@
       <c r="D757" s="0" t="s">
         <v>2145</v>
       </c>
-      <c r="F757" s="0" t="s">
+      <c r="G757" s="0" t="s">
         <v>2146</v>
-      </c>
-      <c r="G757" s="0" t="s">
-        <v>2147</v>
       </c>
     </row>
     <row r="758">
       <c r="D758" s="0" t="s">
+        <v>2147</v>
+      </c>
+      <c r="E758" s="0" t="s">
         <v>2148</v>
       </c>
-      <c r="E758" s="0" t="s">
+      <c r="G758" s="0" t="s">
         <v>2149</v>
-      </c>
-      <c r="G758" s="0" t="s">
-        <v>2150</v>
       </c>
     </row>
     <row r="759">
       <c r="D759" s="0" t="s">
+        <v>2150</v>
+      </c>
+      <c r="E759" s="0" t="s">
         <v>2151</v>
       </c>
-      <c r="E759" s="0" t="s">
+      <c r="G759" s="0" t="s">
         <v>2152</v>
-      </c>
-      <c r="G759" s="0" t="s">
-        <v>2153</v>
       </c>
     </row>
     <row r="760">
       <c r="D760" s="0" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E760" s="0" t="s">
         <v>2154</v>
       </c>
-      <c r="E760" s="0" t="s">
+      <c r="G760" s="0" t="s">
         <v>2155</v>
-      </c>
-      <c r="G760" s="0" t="s">
-        <v>2156</v>
       </c>
     </row>
     <row r="761">
       <c r="D761" s="0" t="s">
+        <v>2156</v>
+      </c>
+      <c r="E761" s="0" t="s">
         <v>2157</v>
       </c>
-      <c r="E761" s="0" t="s">
+      <c r="G761" s="0" t="s">
         <v>2158</v>
-      </c>
-      <c r="G761" s="0" t="s">
-        <v>2159</v>
       </c>
     </row>
     <row r="762">
       <c r="D762" s="0" t="s">
+        <v>2159</v>
+      </c>
+      <c r="E762" s="0" t="s">
         <v>2160</v>
       </c>
-      <c r="E762" s="0" t="s">
+      <c r="G762" s="0" t="s">
         <v>2161</v>
-      </c>
-      <c r="G762" s="0" t="s">
-        <v>2162</v>
       </c>
     </row>
     <row r="763">
       <c r="D763" s="0" t="s">
+        <v>2162</v>
+      </c>
+      <c r="E763" s="0" t="s">
         <v>2163</v>
       </c>
-      <c r="E763" s="0" t="s">
+      <c r="G763" s="0" t="s">
         <v>2164</v>
-      </c>
-      <c r="G763" s="0" t="s">
-        <v>2165</v>
       </c>
     </row>
     <row r="764">
       <c r="D764" s="0" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E764" s="0" t="s">
         <v>2166</v>
       </c>
-      <c r="E764" s="0" t="s">
+      <c r="G764" s="0" t="s">
         <v>2167</v>
-      </c>
-      <c r="G764" s="0" t="s">
-        <v>2168</v>
       </c>
     </row>
     <row r="765">
       <c r="D765" s="0" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E765" s="0" t="s">
+        <v>2168</v>
+      </c>
+      <c r="G765" s="0" t="s">
         <v>2169</v>
-      </c>
-      <c r="E765" s="0" t="s">
-        <v>2169</v>
-      </c>
-      <c r="G765" s="0" t="s">
-        <v>2170</v>
       </c>
     </row>
     <row r="766">
       <c r="D766" s="0" t="s">
+        <v>2170</v>
+      </c>
+      <c r="E766" s="0" t="s">
+        <v>2170</v>
+      </c>
+      <c r="G766" s="0" t="s">
         <v>2171</v>
-      </c>
-      <c r="E766" s="0" t="s">
-        <v>2171</v>
-      </c>
-      <c r="G766" s="0" t="s">
-        <v>2172</v>
       </c>
     </row>
     <row r="767">
       <c r="D767" s="0" t="s">
+        <v>2172</v>
+      </c>
+      <c r="E767" s="0" t="s">
+        <v>2172</v>
+      </c>
+      <c r="G767" s="0" t="s">
         <v>2173</v>
-      </c>
-      <c r="E767" s="0" t="s">
-        <v>2173</v>
-      </c>
-      <c r="G767" s="0" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="768">
       <c r="D768" s="0" t="s">
+        <v>2174</v>
+      </c>
+      <c r="E768" s="0" t="s">
+        <v>2174</v>
+      </c>
+      <c r="G768" s="0" t="s">
         <v>2175</v>
-      </c>
-      <c r="E768" s="0" t="s">
-        <v>2175</v>
-      </c>
-      <c r="G768" s="0" t="s">
-        <v>2176</v>
       </c>
     </row>
     <row r="769">
       <c r="D769" s="0" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E769" s="0" t="s">
+        <v>2176</v>
+      </c>
+      <c r="G769" s="0" t="s">
         <v>2177</v>
-      </c>
-      <c r="E769" s="0" t="s">
-        <v>2177</v>
-      </c>
-      <c r="G769" s="0" t="s">
-        <v>2178</v>
       </c>
     </row>
     <row r="770">
       <c r="D770" s="0" t="s">
+        <v>2178</v>
+      </c>
+      <c r="E770" s="0" t="s">
+        <v>2178</v>
+      </c>
+      <c r="G770" s="0" t="s">
         <v>2179</v>
-      </c>
-      <c r="E770" s="0" t="s">
-        <v>2179</v>
-      </c>
-      <c r="G770" s="0" t="s">
-        <v>2180</v>
       </c>
     </row>
     <row r="771">
       <c r="D771" s="0" t="s">
+        <v>2180</v>
+      </c>
+      <c r="E771" s="0" t="s">
         <v>2181</v>
       </c>
-      <c r="E771" s="0" t="s">
+      <c r="G771" s="0" t="s">
         <v>2182</v>
-      </c>
-      <c r="G771" s="0" t="s">
-        <v>2183</v>
       </c>
     </row>
     <row r="772">
       <c r="D772" s="0" t="s">
+        <v>2183</v>
+      </c>
+      <c r="E772" s="0" t="s">
         <v>2184</v>
       </c>
-      <c r="E772" s="0" t="s">
+      <c r="G772" s="0" t="s">
         <v>2185</v>
-      </c>
-      <c r="G772" s="0" t="s">
-        <v>2186</v>
       </c>
     </row>
     <row r="773">
       <c r="D773" s="0" t="s">
+        <v>2186</v>
+      </c>
+      <c r="E773" s="0" t="s">
         <v>2187</v>
       </c>
-      <c r="E773" s="0" t="s">
+      <c r="G773" s="0" t="s">
         <v>2188</v>
-      </c>
-      <c r="G773" s="0" t="s">
-        <v>2189</v>
       </c>
     </row>
     <row r="774">
       <c r="D774" s="0" t="s">
+        <v>2189</v>
+      </c>
+      <c r="E774" s="0" t="s">
         <v>2190</v>
       </c>
-      <c r="E774" s="0" t="s">
+      <c r="G774" s="0" t="s">
         <v>2191</v>
-      </c>
-      <c r="G774" s="0" t="s">
-        <v>2192</v>
       </c>
     </row>
     <row r="775">
@@ -17296,35 +17149,35 @@
         <v>456</v>
       </c>
       <c r="D775" s="0" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="E775" s="0" t="s">
         <v>1206</v>
       </c>
       <c r="G775" s="0" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="776">
       <c r="D776" s="0" t="s">
+        <v>2194</v>
+      </c>
+      <c r="E776" s="0" t="s">
         <v>2195</v>
       </c>
-      <c r="E776" s="0" t="s">
+      <c r="G776" s="0" t="s">
         <v>2196</v>
-      </c>
-      <c r="G776" s="0" t="s">
-        <v>2197</v>
       </c>
     </row>
     <row r="777">
       <c r="D777" s="0" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="E777" s="0" t="s">
         <v>959</v>
       </c>
       <c r="G777" s="0" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="778">
@@ -17338,7 +17191,7 @@
         <v>26</v>
       </c>
       <c r="D778" s="0" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="779">
@@ -17352,7 +17205,7 @@
         <v>26</v>
       </c>
       <c r="D779" s="0" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="780">
@@ -17366,13 +17219,13 @@
         <v>26</v>
       </c>
       <c r="D780" s="0" t="s">
+        <v>2201</v>
+      </c>
+      <c r="E780" s="0" t="s">
         <v>2202</v>
       </c>
-      <c r="E780" s="0" t="s">
+      <c r="G780" s="0" t="s">
         <v>2203</v>
-      </c>
-      <c r="G780" s="0" t="s">
-        <v>2204</v>
       </c>
     </row>
     <row r="781">
@@ -17386,200 +17239,200 @@
         <v>50</v>
       </c>
       <c r="D781" s="0" t="s">
+        <v>2201</v>
+      </c>
+      <c r="E781" s="0" t="s">
         <v>2202</v>
       </c>
-      <c r="E781" s="0" t="s">
+      <c r="G781" s="0" t="s">
         <v>2203</v>
-      </c>
-      <c r="G781" s="0" t="s">
-        <v>2204</v>
       </c>
     </row>
     <row r="782">
       <c r="D782" s="0" t="s">
+        <v>2204</v>
+      </c>
+      <c r="E782" s="0" t="s">
         <v>2205</v>
       </c>
-      <c r="E782" s="0" t="s">
+      <c r="G782" s="0" t="s">
         <v>2206</v>
-      </c>
-      <c r="G782" s="0" t="s">
-        <v>2207</v>
       </c>
     </row>
     <row r="783">
       <c r="D783" s="0" t="s">
+        <v>2207</v>
+      </c>
+      <c r="E783" s="0" t="s">
         <v>2208</v>
       </c>
-      <c r="E783" s="0" t="s">
+      <c r="G783" s="0" t="s">
         <v>2209</v>
-      </c>
-      <c r="G783" s="0" t="s">
-        <v>2210</v>
       </c>
     </row>
     <row r="784">
       <c r="D784" s="0" t="s">
+        <v>2210</v>
+      </c>
+      <c r="E784" s="0" t="s">
         <v>2211</v>
       </c>
-      <c r="E784" s="0" t="s">
+      <c r="G784" s="0" t="s">
         <v>2212</v>
-      </c>
-      <c r="G784" s="0" t="s">
-        <v>2213</v>
       </c>
     </row>
     <row r="785">
       <c r="D785" s="0" t="s">
+        <v>2213</v>
+      </c>
+      <c r="E785" s="0" t="s">
         <v>2214</v>
       </c>
-      <c r="E785" s="0" t="s">
+      <c r="G785" s="0" t="s">
         <v>2215</v>
-      </c>
-      <c r="G785" s="0" t="s">
-        <v>2216</v>
       </c>
     </row>
     <row r="786">
       <c r="D786" s="0" t="s">
+        <v>2216</v>
+      </c>
+      <c r="E786" s="0" t="s">
         <v>2217</v>
       </c>
-      <c r="E786" s="0" t="s">
+      <c r="G786" s="0" t="s">
         <v>2218</v>
-      </c>
-      <c r="G786" s="0" t="s">
-        <v>2219</v>
       </c>
     </row>
     <row r="787">
       <c r="D787" s="0" t="s">
+        <v>2219</v>
+      </c>
+      <c r="E787" s="0" t="s">
         <v>2220</v>
       </c>
-      <c r="E787" s="0" t="s">
+      <c r="G787" s="0" t="s">
         <v>2221</v>
-      </c>
-      <c r="G787" s="0" t="s">
-        <v>2222</v>
       </c>
     </row>
     <row r="788">
       <c r="D788" s="0" t="s">
+        <v>2222</v>
+      </c>
+      <c r="E788" s="0" t="s">
         <v>2223</v>
       </c>
-      <c r="E788" s="0" t="s">
+      <c r="G788" s="0" t="s">
         <v>2224</v>
-      </c>
-      <c r="G788" s="0" t="s">
-        <v>2225</v>
       </c>
     </row>
     <row r="789">
       <c r="D789" s="0" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E789" s="0" t="s">
         <v>2226</v>
       </c>
-      <c r="E789" s="0" t="s">
+      <c r="G789" s="0" t="s">
         <v>2227</v>
-      </c>
-      <c r="G789" s="0" t="s">
-        <v>2228</v>
       </c>
     </row>
     <row r="790">
       <c r="D790" s="0" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E790" s="0" t="s">
         <v>2229</v>
       </c>
-      <c r="E790" s="0" t="s">
+      <c r="G790" s="0" t="s">
         <v>2230</v>
-      </c>
-      <c r="G790" s="0" t="s">
-        <v>2231</v>
       </c>
     </row>
     <row r="791">
       <c r="D791" s="0" t="s">
+        <v>2231</v>
+      </c>
+      <c r="E791" s="0" t="s">
         <v>2232</v>
       </c>
-      <c r="E791" s="0" t="s">
+      <c r="G791" s="0" t="s">
         <v>2233</v>
-      </c>
-      <c r="G791" s="0" t="s">
-        <v>2234</v>
       </c>
     </row>
     <row r="792">
       <c r="D792" s="0" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E792" s="0" t="s">
         <v>2235</v>
       </c>
-      <c r="E792" s="0" t="s">
+      <c r="G792" s="0" t="s">
         <v>2236</v>
-      </c>
-      <c r="G792" s="0" t="s">
-        <v>2237</v>
       </c>
     </row>
     <row r="793">
       <c r="D793" s="0" t="s">
+        <v>2237</v>
+      </c>
+      <c r="E793" s="0" t="s">
         <v>2238</v>
       </c>
-      <c r="E793" s="0" t="s">
+      <c r="G793" s="0" t="s">
         <v>2239</v>
-      </c>
-      <c r="G793" s="0" t="s">
-        <v>2240</v>
       </c>
     </row>
     <row r="794">
       <c r="D794" s="0" t="s">
+        <v>2240</v>
+      </c>
+      <c r="E794" s="0" t="s">
         <v>2241</v>
       </c>
-      <c r="E794" s="0" t="s">
+      <c r="G794" s="0" t="s">
         <v>2242</v>
-      </c>
-      <c r="G794" s="0" t="s">
-        <v>2243</v>
       </c>
     </row>
     <row r="795">
       <c r="D795" s="0" t="s">
+        <v>2243</v>
+      </c>
+      <c r="E795" s="0" t="s">
         <v>2244</v>
       </c>
-      <c r="E795" s="0" t="s">
+      <c r="G795" s="0" t="s">
         <v>2245</v>
-      </c>
-      <c r="G795" s="0" t="s">
-        <v>2246</v>
       </c>
     </row>
     <row r="796">
       <c r="D796" s="0" t="s">
+        <v>2246</v>
+      </c>
+      <c r="E796" s="0" t="s">
         <v>2247</v>
       </c>
-      <c r="E796" s="0" t="s">
+      <c r="G796" s="0" t="s">
         <v>2248</v>
-      </c>
-      <c r="G796" s="0" t="s">
-        <v>2249</v>
       </c>
     </row>
     <row r="797">
       <c r="D797" s="0" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E797" s="0" t="s">
         <v>2250</v>
       </c>
-      <c r="E797" s="0" t="s">
+      <c r="G797" s="0" t="s">
         <v>2251</v>
-      </c>
-      <c r="G797" s="0" t="s">
-        <v>2252</v>
       </c>
     </row>
     <row r="798">
       <c r="D798" s="0" t="s">
+        <v>2252</v>
+      </c>
+      <c r="E798" s="0" t="s">
         <v>2253</v>
       </c>
-      <c r="E798" s="0" t="s">
+      <c r="G798" s="0" t="s">
         <v>2254</v>
-      </c>
-      <c r="G798" s="0" t="s">
-        <v>2255</v>
       </c>
     </row>
     <row r="799">
@@ -17593,189 +17446,189 @@
         <v>594</v>
       </c>
       <c r="D799" s="0" t="s">
+        <v>2255</v>
+      </c>
+      <c r="E799" s="0" t="s">
         <v>2256</v>
       </c>
-      <c r="E799" s="0" t="s">
+      <c r="G799" s="0" t="s">
         <v>2257</v>
-      </c>
-      <c r="G799" s="0" t="s">
-        <v>2258</v>
       </c>
     </row>
     <row r="800">
       <c r="D800" s="0" t="s">
+        <v>2258</v>
+      </c>
+      <c r="E800" s="0" t="s">
         <v>2259</v>
       </c>
-      <c r="E800" s="0" t="s">
+      <c r="G800" s="0" t="s">
         <v>2260</v>
-      </c>
-      <c r="G800" s="0" t="s">
-        <v>2261</v>
       </c>
     </row>
     <row r="801">
       <c r="D801" s="0" t="s">
+        <v>2261</v>
+      </c>
+      <c r="E801" s="0" t="s">
         <v>2262</v>
       </c>
-      <c r="E801" s="0" t="s">
+      <c r="G801" s="0" t="s">
         <v>2263</v>
-      </c>
-      <c r="G801" s="0" t="s">
-        <v>2264</v>
       </c>
     </row>
     <row r="802">
       <c r="D802" s="0" t="s">
+        <v>2264</v>
+      </c>
+      <c r="E802" s="0" t="s">
         <v>2265</v>
       </c>
-      <c r="E802" s="0" t="s">
+      <c r="G802" s="0" t="s">
         <v>2266</v>
-      </c>
-      <c r="G802" s="0" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="803">
       <c r="D803" s="0" t="s">
+        <v>2267</v>
+      </c>
+      <c r="E803" s="0" t="s">
         <v>2268</v>
       </c>
-      <c r="E803" s="0" t="s">
+      <c r="G803" s="0" t="s">
         <v>2269</v>
-      </c>
-      <c r="G803" s="0" t="s">
-        <v>2270</v>
       </c>
     </row>
     <row r="804">
       <c r="D804" s="0" t="s">
+        <v>2270</v>
+      </c>
+      <c r="E804" s="0" t="s">
         <v>2271</v>
       </c>
-      <c r="E804" s="0" t="s">
+      <c r="G804" s="0" t="s">
         <v>2272</v>
-      </c>
-      <c r="G804" s="0" t="s">
-        <v>2273</v>
       </c>
     </row>
     <row r="805">
       <c r="D805" s="0" t="s">
+        <v>2273</v>
+      </c>
+      <c r="E805" s="0" t="s">
         <v>2274</v>
       </c>
-      <c r="E805" s="0" t="s">
+      <c r="G805" s="0" t="s">
         <v>2275</v>
-      </c>
-      <c r="G805" s="0" t="s">
-        <v>2276</v>
       </c>
     </row>
     <row r="806">
       <c r="D806" s="0" t="s">
+        <v>2276</v>
+      </c>
+      <c r="E806" s="0" t="s">
+        <v>2276</v>
+      </c>
+      <c r="G806" s="0" t="s">
         <v>2277</v>
-      </c>
-      <c r="E806" s="0" t="s">
-        <v>2277</v>
-      </c>
-      <c r="G806" s="0" t="s">
-        <v>2278</v>
       </c>
     </row>
     <row r="807">
       <c r="D807" s="0" t="s">
+        <v>2278</v>
+      </c>
+      <c r="E807" s="0" t="s">
         <v>2279</v>
       </c>
-      <c r="E807" s="0" t="s">
+      <c r="G807" s="0" t="s">
         <v>2280</v>
-      </c>
-      <c r="G807" s="0" t="s">
-        <v>2281</v>
       </c>
     </row>
     <row r="808">
       <c r="D808" s="0" t="s">
+        <v>2281</v>
+      </c>
+      <c r="E808" s="0" t="s">
         <v>2282</v>
       </c>
-      <c r="E808" s="0" t="s">
+      <c r="G808" s="0" t="s">
         <v>2283</v>
-      </c>
-      <c r="G808" s="0" t="s">
-        <v>2284</v>
       </c>
     </row>
     <row r="809">
       <c r="D809" s="0" t="s">
+        <v>2284</v>
+      </c>
+      <c r="E809" s="0" t="s">
         <v>2285</v>
       </c>
-      <c r="E809" s="0" t="s">
+      <c r="G809" s="0" t="s">
         <v>2286</v>
-      </c>
-      <c r="G809" s="0" t="s">
-        <v>2287</v>
       </c>
     </row>
     <row r="810">
       <c r="D810" s="0" t="s">
+        <v>2287</v>
+      </c>
+      <c r="E810" s="0" t="s">
         <v>2288</v>
       </c>
-      <c r="E810" s="0" t="s">
+      <c r="G810" s="0" t="s">
         <v>2289</v>
-      </c>
-      <c r="G810" s="0" t="s">
-        <v>2290</v>
       </c>
     </row>
     <row r="811">
       <c r="D811" s="0" t="s">
+        <v>2290</v>
+      </c>
+      <c r="E811" s="0" t="s">
+        <v>2290</v>
+      </c>
+      <c r="G811" s="0" t="s">
         <v>2291</v>
-      </c>
-      <c r="E811" s="0" t="s">
-        <v>2291</v>
-      </c>
-      <c r="G811" s="0" t="s">
-        <v>2292</v>
       </c>
     </row>
     <row r="812">
       <c r="D812" s="0" t="s">
+        <v>2292</v>
+      </c>
+      <c r="E812" s="0" t="s">
+        <v>2292</v>
+      </c>
+      <c r="G812" s="0" t="s">
         <v>2293</v>
-      </c>
-      <c r="E812" s="0" t="s">
-        <v>2293</v>
-      </c>
-      <c r="G812" s="0" t="s">
-        <v>2294</v>
       </c>
     </row>
     <row r="813">
       <c r="D813" s="0" t="s">
+        <v>2294</v>
+      </c>
+      <c r="E813" s="0" t="s">
+        <v>2294</v>
+      </c>
+      <c r="G813" s="0" t="s">
         <v>2295</v>
-      </c>
-      <c r="E813" s="0" t="s">
-        <v>2295</v>
-      </c>
-      <c r="G813" s="0" t="s">
-        <v>2296</v>
       </c>
     </row>
     <row r="814">
       <c r="D814" s="0" t="s">
+        <v>2296</v>
+      </c>
+      <c r="E814" s="0" t="s">
+        <v>2296</v>
+      </c>
+      <c r="G814" s="0" t="s">
         <v>2297</v>
-      </c>
-      <c r="E814" s="0" t="s">
-        <v>2297</v>
-      </c>
-      <c r="G814" s="0" t="s">
-        <v>2298</v>
       </c>
     </row>
     <row r="815">
       <c r="D815" s="0" t="s">
+        <v>2298</v>
+      </c>
+      <c r="E815" s="0" t="s">
         <v>2299</v>
       </c>
-      <c r="E815" s="0" t="s">
+      <c r="G815" s="0" t="s">
         <v>2300</v>
-      </c>
-      <c r="G815" s="0" t="s">
-        <v>2301</v>
       </c>
     </row>
     <row r="816">
@@ -17786,16 +17639,16 @@
         <v>26</v>
       </c>
       <c r="C816" s="0" t="s">
+        <v>2301</v>
+      </c>
+      <c r="D816" s="0" t="s">
         <v>2302</v>
       </c>
-      <c r="D816" s="0" t="s">
+      <c r="E816" s="0" t="s">
         <v>2303</v>
       </c>
-      <c r="E816" s="0" t="s">
+      <c r="G816" s="0" t="s">
         <v>2304</v>
-      </c>
-      <c r="G816" s="0" t="s">
-        <v>2305</v>
       </c>
     </row>
     <row r="817">
@@ -17806,16 +17659,16 @@
         <v>26</v>
       </c>
       <c r="C817" s="0" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="D817" s="0" t="s">
+        <v>2305</v>
+      </c>
+      <c r="E817" s="0" t="s">
         <v>2306</v>
       </c>
-      <c r="E817" s="0" t="s">
+      <c r="G817" s="0" t="s">
         <v>2307</v>
-      </c>
-      <c r="G817" s="0" t="s">
-        <v>2308</v>
       </c>
     </row>
     <row r="818">
@@ -17826,197 +17679,197 @@
         <v>26</v>
       </c>
       <c r="C818" s="0" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="D818" s="0" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="819">
       <c r="D819" s="0" t="s">
+        <v>2309</v>
+      </c>
+      <c r="E819" s="0" t="s">
         <v>2310</v>
       </c>
-      <c r="E819" s="0" t="s">
+      <c r="G819" s="0" t="s">
         <v>2311</v>
-      </c>
-      <c r="G819" s="0" t="s">
-        <v>2312</v>
       </c>
     </row>
     <row r="820">
       <c r="D820" s="0" t="s">
+        <v>2312</v>
+      </c>
+      <c r="E820" s="0" t="s">
         <v>2313</v>
       </c>
-      <c r="E820" s="0" t="s">
+      <c r="G820" s="0" t="s">
         <v>2314</v>
-      </c>
-      <c r="G820" s="0" t="s">
-        <v>2315</v>
       </c>
     </row>
     <row r="821">
       <c r="D821" s="0" t="s">
+        <v>2315</v>
+      </c>
+      <c r="E821" s="0" t="s">
         <v>2316</v>
       </c>
-      <c r="E821" s="0" t="s">
+      <c r="G821" s="0" t="s">
         <v>2317</v>
-      </c>
-      <c r="G821" s="0" t="s">
-        <v>2318</v>
       </c>
     </row>
     <row r="822">
       <c r="D822" s="0" t="s">
+        <v>2318</v>
+      </c>
+      <c r="E822" s="0" t="s">
         <v>2319</v>
       </c>
-      <c r="E822" s="0" t="s">
+      <c r="G822" s="0" t="s">
         <v>2320</v>
-      </c>
-      <c r="G822" s="0" t="s">
-        <v>2321</v>
       </c>
     </row>
     <row r="823">
       <c r="D823" s="0" t="s">
+        <v>2321</v>
+      </c>
+      <c r="E823" s="0" t="s">
         <v>2322</v>
       </c>
-      <c r="E823" s="0" t="s">
+      <c r="G823" s="0" t="s">
         <v>2323</v>
-      </c>
-      <c r="G823" s="0" t="s">
-        <v>2324</v>
       </c>
     </row>
     <row r="824">
       <c r="D824" s="0" t="s">
+        <v>2324</v>
+      </c>
+      <c r="E824" s="0" t="s">
         <v>2325</v>
       </c>
-      <c r="E824" s="0" t="s">
+      <c r="G824" s="0" t="s">
         <v>2326</v>
-      </c>
-      <c r="G824" s="0" t="s">
-        <v>2327</v>
       </c>
     </row>
     <row r="825">
       <c r="D825" s="0" t="s">
+        <v>2327</v>
+      </c>
+      <c r="E825" s="0" t="s">
         <v>2328</v>
       </c>
-      <c r="E825" s="0" t="s">
+      <c r="G825" s="0" t="s">
         <v>2329</v>
-      </c>
-      <c r="G825" s="0" t="s">
-        <v>2330</v>
       </c>
     </row>
     <row r="826">
       <c r="D826" s="0" t="s">
+        <v>2330</v>
+      </c>
+      <c r="E826" s="0" t="s">
         <v>2331</v>
       </c>
-      <c r="E826" s="0" t="s">
+      <c r="G826" s="0" t="s">
         <v>2332</v>
-      </c>
-      <c r="G826" s="0" t="s">
-        <v>2333</v>
       </c>
     </row>
     <row r="827">
       <c r="D827" s="0" t="s">
+        <v>2333</v>
+      </c>
+      <c r="E827" s="0" t="s">
         <v>2334</v>
       </c>
-      <c r="E827" s="0" t="s">
+      <c r="G827" s="0" t="s">
         <v>2335</v>
-      </c>
-      <c r="G827" s="0" t="s">
-        <v>2336</v>
       </c>
     </row>
     <row r="828">
       <c r="D828" s="0" t="s">
+        <v>2336</v>
+      </c>
+      <c r="E828" s="0" t="s">
         <v>2337</v>
       </c>
-      <c r="E828" s="0" t="s">
+      <c r="G828" s="0" t="s">
         <v>2338</v>
-      </c>
-      <c r="G828" s="0" t="s">
-        <v>2339</v>
       </c>
     </row>
     <row r="829">
       <c r="D829" s="0" t="s">
+        <v>2339</v>
+      </c>
+      <c r="E829" s="0" t="s">
         <v>2340</v>
       </c>
-      <c r="E829" s="0" t="s">
+      <c r="G829" s="0" t="s">
         <v>2341</v>
-      </c>
-      <c r="G829" s="0" t="s">
-        <v>2342</v>
       </c>
     </row>
     <row r="830">
       <c r="D830" s="0" t="s">
+        <v>2342</v>
+      </c>
+      <c r="E830" s="0" t="s">
         <v>2343</v>
       </c>
-      <c r="E830" s="0" t="s">
+      <c r="G830" s="0" t="s">
         <v>2344</v>
-      </c>
-      <c r="G830" s="0" t="s">
-        <v>2345</v>
       </c>
     </row>
     <row r="831">
       <c r="D831" s="0" t="s">
+        <v>2345</v>
+      </c>
+      <c r="E831" s="0" t="s">
         <v>2346</v>
       </c>
-      <c r="E831" s="0" t="s">
+      <c r="G831" s="0" t="s">
         <v>2347</v>
-      </c>
-      <c r="G831" s="0" t="s">
-        <v>2348</v>
       </c>
     </row>
     <row r="832">
       <c r="D832" s="0" t="s">
+        <v>2348</v>
+      </c>
+      <c r="E832" s="0" t="s">
         <v>2349</v>
       </c>
-      <c r="E832" s="0" t="s">
+      <c r="G832" s="0" t="s">
         <v>2350</v>
-      </c>
-      <c r="G832" s="0" t="s">
-        <v>2351</v>
       </c>
     </row>
     <row r="833">
       <c r="D833" s="0" t="s">
+        <v>2351</v>
+      </c>
+      <c r="E833" s="0" t="s">
         <v>2352</v>
       </c>
-      <c r="E833" s="0" t="s">
+      <c r="G833" s="0" t="s">
         <v>2353</v>
-      </c>
-      <c r="G833" s="0" t="s">
-        <v>2354</v>
       </c>
     </row>
     <row r="834">
       <c r="D834" s="0" t="s">
+        <v>2354</v>
+      </c>
+      <c r="E834" s="0" t="s">
         <v>2355</v>
       </c>
-      <c r="E834" s="0" t="s">
+      <c r="G834" s="0" t="s">
         <v>2356</v>
-      </c>
-      <c r="G834" s="0" t="s">
-        <v>2357</v>
       </c>
     </row>
     <row r="835">
       <c r="D835" s="0" t="s">
+        <v>2357</v>
+      </c>
+      <c r="E835" s="0" t="s">
         <v>2358</v>
       </c>
-      <c r="E835" s="0" t="s">
+      <c r="G835" s="0" t="s">
         <v>2359</v>
-      </c>
-      <c r="G835" s="0" t="s">
-        <v>2360</v>
       </c>
     </row>
     <row r="836">
@@ -18027,7 +17880,7 @@
         <v>1109</v>
       </c>
       <c r="D836" s="0" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="837">
@@ -18049,7 +17902,7 @@
         <v>73</v>
       </c>
       <c r="D838" s="0" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="839">
@@ -18071,7 +17924,7 @@
         <v>377</v>
       </c>
       <c r="D840" s="0" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="841">
@@ -18082,7 +17935,7 @@
         <v>594</v>
       </c>
       <c r="D841" s="0" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="842">
@@ -18093,7 +17946,7 @@
         <v>26</v>
       </c>
       <c r="D842" s="0" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="843">
@@ -18104,7 +17957,7 @@
         <v>26</v>
       </c>
       <c r="D843" s="0" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="844">
@@ -18115,7 +17968,7 @@
         <v>26</v>
       </c>
       <c r="D844" s="0" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="845">
@@ -18126,7 +17979,7 @@
         <v>26</v>
       </c>
       <c r="D845" s="0" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="846">
@@ -18137,7 +17990,7 @@
         <v>26</v>
       </c>
       <c r="D846" s="0" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="847">
@@ -18148,7 +18001,7 @@
         <v>26</v>
       </c>
       <c r="D847" s="0" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="848">
@@ -18159,7 +18012,7 @@
         <v>1152</v>
       </c>
       <c r="D848" s="0" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="849">
@@ -18170,7 +18023,7 @@
         <v>26</v>
       </c>
       <c r="D849" s="0" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="850">
@@ -18181,7 +18034,7 @@
         <v>26</v>
       </c>
       <c r="D850" s="0" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="851">
@@ -18192,7 +18045,7 @@
         <v>26</v>
       </c>
       <c r="D851" s="0" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="852">
@@ -18203,7 +18056,7 @@
         <v>26</v>
       </c>
       <c r="D852" s="0" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="853">
@@ -18214,7 +18067,7 @@
         <v>26</v>
       </c>
       <c r="D853" s="0" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="854">
@@ -18236,7 +18089,7 @@
         <v>26</v>
       </c>
       <c r="D855" s="0" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="856">
@@ -18247,7 +18100,7 @@
         <v>594</v>
       </c>
       <c r="D856" s="0" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="857">
@@ -18280,7 +18133,7 @@
         <v>456</v>
       </c>
       <c r="D859" s="0" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="860">
@@ -18302,7 +18155,7 @@
         <v>1152</v>
       </c>
       <c r="D861" s="0" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="862">
@@ -18324,7 +18177,7 @@
         <v>737</v>
       </c>
       <c r="D863" s="0" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="864">
@@ -18335,7 +18188,7 @@
         <v>377</v>
       </c>
       <c r="D864" s="0" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="865">
@@ -18401,7 +18254,7 @@
         <v>377</v>
       </c>
       <c r="D870" s="0" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="871">
@@ -18483,10 +18336,10 @@
     </row>
     <row r="878">
       <c r="B878" s="0" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C878" s="0" t="s">
         <v>2381</v>
-      </c>
-      <c r="C878" s="0" t="s">
-        <v>2382</v>
       </c>
       <c r="D878" s="0" t="s">
         <v>2066</v>
@@ -18494,7 +18347,7 @@
     </row>
     <row r="879">
       <c r="B879" s="0" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="C879" s="0" t="s">
         <v>450</v>
@@ -18511,7 +18364,7 @@
         <v>26</v>
       </c>
       <c r="D880" s="0" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="881">
@@ -18533,7 +18386,7 @@
         <v>26</v>
       </c>
       <c r="D882" s="0" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="883">
@@ -18555,7 +18408,7 @@
         <v>26</v>
       </c>
       <c r="D884" s="0" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="885">
@@ -18585,10 +18438,10 @@
         <v>117</v>
       </c>
       <c r="C887" s="0" t="s">
+        <v>2386</v>
+      </c>
+      <c r="D887" s="0" t="s">
         <v>2387</v>
-      </c>
-      <c r="D887" s="0" t="s">
-        <v>2388</v>
       </c>
     </row>
     <row r="888">
@@ -18596,10 +18449,10 @@
         <v>117</v>
       </c>
       <c r="C888" s="0" t="s">
+        <v>2388</v>
+      </c>
+      <c r="D888" s="0" t="s">
         <v>2389</v>
-      </c>
-      <c r="D888" s="0" t="s">
-        <v>2390</v>
       </c>
     </row>
     <row r="889">
@@ -18607,10 +18460,10 @@
         <v>117</v>
       </c>
       <c r="C889" s="0" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="D889" s="0" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="890">
@@ -18618,10 +18471,10 @@
         <v>117</v>
       </c>
       <c r="C890" s="0" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="D890" s="0" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="891">
@@ -18629,21 +18482,21 @@
         <v>117</v>
       </c>
       <c r="C891" s="0" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="D891" s="0" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="892">
       <c r="B892" s="0" t="s">
+        <v>2393</v>
+      </c>
+      <c r="C892" s="0" t="s">
         <v>2394</v>
       </c>
-      <c r="C892" s="0" t="s">
+      <c r="D892" s="0" t="s">
         <v>2395</v>
-      </c>
-      <c r="D892" s="0" t="s">
-        <v>2396</v>
       </c>
     </row>
     <row r="893">
@@ -18651,21 +18504,21 @@
         <v>117</v>
       </c>
       <c r="C893" s="0" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="D893" s="0" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="894">
       <c r="B894" s="0" t="s">
+        <v>2397</v>
+      </c>
+      <c r="C894" s="0" t="s">
         <v>2398</v>
       </c>
-      <c r="C894" s="0" t="s">
+      <c r="D894" s="0" t="s">
         <v>2399</v>
-      </c>
-      <c r="D894" s="0" t="s">
-        <v>2400</v>
       </c>
     </row>
     <row r="895">
@@ -18676,7 +18529,7 @@
         <v>456</v>
       </c>
       <c r="D895" s="0" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="896">
@@ -18720,7 +18573,7 @@
         <v>1152</v>
       </c>
       <c r="D899" s="0" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="900">
@@ -18731,7 +18584,7 @@
         <v>73</v>
       </c>
       <c r="D900" s="0" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="901">
@@ -18753,7 +18606,7 @@
         <v>73</v>
       </c>
       <c r="D902" s="0" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="903">
@@ -18764,7 +18617,7 @@
         <v>737</v>
       </c>
       <c r="D903" s="0" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="904">
@@ -18786,7 +18639,7 @@
         <v>73</v>
       </c>
       <c r="D905" s="0" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="906">
@@ -18798,6 +18651,309 @@
       </c>
       <c r="D906" s="0" t="s">
         <v>1729</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="B907" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C907" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D907" s="0" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B908" s="0" t="s">
+        <v>2144</v>
+      </c>
+      <c r="C908" s="0" t="s">
+        <v>2404</v>
+      </c>
+      <c r="D908" s="0" t="s">
+        <v>2405</v>
+      </c>
+      <c r="G908" s="0" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="B909" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="C909" s="0" t="s">
+        <v>456</v>
+      </c>
+      <c r="D909" s="0" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="B910" s="0" t="s">
+        <v>2407</v>
+      </c>
+      <c r="C910" s="0" t="s">
+        <v>2408</v>
+      </c>
+      <c r="D910" s="0" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="B911" s="0" t="s">
+        <v>2409</v>
+      </c>
+      <c r="C911" s="0" t="s">
+        <v>2410</v>
+      </c>
+      <c r="D911" s="0" t="s">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="B912" s="0" t="s">
+        <v>2409</v>
+      </c>
+      <c r="C912" s="0" t="s">
+        <v>2410</v>
+      </c>
+      <c r="D912" s="0" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="B913" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="C913" s="0" t="s">
+        <v>594</v>
+      </c>
+      <c r="D913" s="0" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="B914" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="C914" s="0" t="s">
+        <v>737</v>
+      </c>
+      <c r="D914" s="0" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="B915" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="C915" s="0" t="s">
+        <v>2414</v>
+      </c>
+      <c r="D915" s="0" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="B916" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="C916" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="D916" s="0" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="B917" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="C917" s="0" t="s">
+        <v>737</v>
+      </c>
+      <c r="D917" s="0" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="B918" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="C918" s="0" t="s">
+        <v>456</v>
+      </c>
+      <c r="D918" s="0" t="s">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="B919" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="C919" s="0" t="s">
+        <v>456</v>
+      </c>
+      <c r="D919" s="0" t="s">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="B920" s="0" t="s">
+        <v>2409</v>
+      </c>
+      <c r="C920" s="0" t="s">
+        <v>2410</v>
+      </c>
+      <c r="D920" s="0" t="s">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="B921" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C921" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D921" s="0" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="B922" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C922" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D922" s="0" t="s">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="B923" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C923" s="0" t="s">
+        <v>737</v>
+      </c>
+      <c r="D923" s="0" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="B924" s="0" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C924" s="0" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D924" s="0" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="B925" s="0" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C925" s="0" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D925" s="0" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="B926" s="0" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C926" s="0" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D926" s="0" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="B927" s="0" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C927" s="0" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D927" s="0" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="B928" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C928" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D928" s="0" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="B929" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C929" s="0" t="s">
+        <v>737</v>
+      </c>
+      <c r="D929" s="0" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="B930" s="0" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C930" s="0" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D930" s="0" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="B931" s="0" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C931" s="0" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D931" s="0" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="B932" s="0" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C932" s="0" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D932" s="0" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="B933" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C933" s="0" t="s">
+        <v>737</v>
+      </c>
+      <c r="D933" s="0" t="s">
+        <v>768</v>
       </c>
     </row>
   </sheetData>

--- a/Source/Data/UALAllOperations.xlsx
+++ b/Source/Data/UALAllOperations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2417" uniqueCount="2417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2430" uniqueCount="2430">
   <si>
     <t>Risk</t>
   </si>
@@ -7271,6 +7271,45 @@
   </si>
   <si>
     <t>Update device.</t>
+  </si>
+  <si>
+    <t>Discovery</t>
+  </si>
+  <si>
+    <t>ViewedSearchResultsPurged</t>
+  </si>
+  <si>
+    <t>Get-ComplianceSearchAction</t>
+  </si>
+  <si>
+    <t>SearchResultsPurged</t>
+  </si>
+  <si>
+    <t>New-ComplianceSearchAction</t>
+  </si>
+  <si>
+    <t>Get-ComplianceSearch</t>
+  </si>
+  <si>
+    <t>SearchViewed</t>
+  </si>
+  <si>
+    <t>SearchRemoved</t>
+  </si>
+  <si>
+    <t>Remove-ComplianceSearch</t>
+  </si>
+  <si>
+    <t>SearchStarted</t>
+  </si>
+  <si>
+    <t>Start-ComplianceSearch</t>
+  </si>
+  <si>
+    <t>SearchCreated</t>
+  </si>
+  <si>
+    <t>New-ComplianceSearch</t>
   </si>
 </sst>
 </file>
@@ -7857,8 +7896,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}" name="Table1" displayName="Table1" ref="A1:G933" totalsRowShown="0">
-  <autoFilter ref="A1:G931" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}" name="Table1" displayName="Table1" ref="A1:G946" totalsRowShown="0">
+  <autoFilter ref="A1:G934" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G835">
     <sortCondition ref="D2:D835"/>
   </sortState>
@@ -8192,7 +8231,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{207B3246-3E1F-4883-B5B7-F0312ED8EA41}">
-  <dimension ref="A1:G933"/>
+  <dimension ref="A1:G946"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="8.140625" customWidth="1"/>
@@ -18954,6 +18993,149 @@
       </c>
       <c r="D933" s="0" t="s">
         <v>768</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="B934" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="C934" s="0" t="s">
+        <v>594</v>
+      </c>
+      <c r="D934" s="0" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="B935" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C935" s="0" t="s">
+        <v>2417</v>
+      </c>
+      <c r="D935" s="0" t="s">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="B936" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C936" s="0" t="s">
+        <v>2388</v>
+      </c>
+      <c r="D936" s="0" t="s">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="B937" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C937" s="0" t="s">
+        <v>2417</v>
+      </c>
+      <c r="D937" s="0" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="B938" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C938" s="0" t="s">
+        <v>2388</v>
+      </c>
+      <c r="D938" s="0" t="s">
+        <v>2421</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="B939" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C939" s="0" t="s">
+        <v>2388</v>
+      </c>
+      <c r="D939" s="0" t="s">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="B940" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C940" s="0" t="s">
+        <v>2417</v>
+      </c>
+      <c r="D940" s="0" t="s">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="B941" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C941" s="0" t="s">
+        <v>2417</v>
+      </c>
+      <c r="D941" s="0" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="B942" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C942" s="0" t="s">
+        <v>2388</v>
+      </c>
+      <c r="D942" s="0" t="s">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="B943" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C943" s="0" t="s">
+        <v>2417</v>
+      </c>
+      <c r="D943" s="0" t="s">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="B944" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C944" s="0" t="s">
+        <v>2388</v>
+      </c>
+      <c r="D944" s="0" t="s">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="B945" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C945" s="0" t="s">
+        <v>2417</v>
+      </c>
+      <c r="D945" s="0" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="B946" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C946" s="0" t="s">
+        <v>2388</v>
+      </c>
+      <c r="D946" s="0" t="s">
+        <v>2429</v>
       </c>
     </row>
   </sheetData>

--- a/Source/Data/UALAllOperations.xlsx
+++ b/Source/Data/UALAllOperations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2430" uniqueCount="2430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2432" uniqueCount="2432">
   <si>
     <t>Risk</t>
   </si>
@@ -7310,6 +7310,12 @@
   </si>
   <si>
     <t>New-ComplianceSearch</t>
+  </si>
+  <si>
+    <t>FileBlocked</t>
+  </si>
+  <si>
+    <t>AccessRequestApproved</t>
   </si>
 </sst>
 </file>
@@ -7896,8 +7902,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}" name="Table1" displayName="Table1" ref="A1:G946" totalsRowShown="0">
-  <autoFilter ref="A1:G934" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}" name="Table1" displayName="Table1" ref="A1:G952" totalsRowShown="0">
+  <autoFilter ref="A1:G947" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G835">
     <sortCondition ref="D2:D835"/>
   </sortState>
@@ -8231,7 +8237,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{207B3246-3E1F-4883-B5B7-F0312ED8EA41}">
-  <dimension ref="A1:G946"/>
+  <dimension ref="A1:G952"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="8.140625" customWidth="1"/>
@@ -19136,6 +19142,72 @@
       </c>
       <c r="D946" s="0" t="s">
         <v>2429</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="B947" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C947" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D947" s="0" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="B948" s="0" t="s">
+        <v>2409</v>
+      </c>
+      <c r="C948" s="0" t="s">
+        <v>2410</v>
+      </c>
+      <c r="D948" s="0" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="B949" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="C949" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="D949" s="0" t="s">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="B950" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="C950" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="D950" s="0" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="B951" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C951" s="0" t="s">
+        <v>737</v>
+      </c>
+      <c r="D951" s="0" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="B952" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C952" s="0" t="s">
+        <v>737</v>
+      </c>
+      <c r="D952" s="0" t="s">
+        <v>857</v>
       </c>
     </row>
   </sheetData>

--- a/Source/Data/UALAllOperations.xlsx
+++ b/Source/Data/UALAllOperations.xlsx
@@ -7902,8 +7902,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}" name="Table1" displayName="Table1" ref="A1:G952" totalsRowShown="0">
-  <autoFilter ref="A1:G947" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}" name="Table1" displayName="Table1" ref="A1:G953" totalsRowShown="0">
+  <autoFilter ref="A1:G952" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G835">
     <sortCondition ref="D2:D835"/>
   </sortState>
@@ -8237,7 +8237,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{207B3246-3E1F-4883-B5B7-F0312ED8EA41}">
-  <dimension ref="A1:G952"/>
+  <dimension ref="A1:G953"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="8.140625" customWidth="1"/>
@@ -19208,6 +19208,17 @@
       </c>
       <c r="D952" s="0" t="s">
         <v>857</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="B953" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C953" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D953" s="0" t="s">
+        <v>1162</v>
       </c>
     </row>
   </sheetData>

--- a/Source/Data/UALAllOperations.xlsx
+++ b/Source/Data/UALAllOperations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2432" uniqueCount="2432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2433" uniqueCount="2433">
   <si>
     <t>Risk</t>
   </si>
@@ -7316,6 +7316,9 @@
   </si>
   <si>
     <t>AccessRequestApproved</t>
+  </si>
+  <si>
+    <t>AuditSearch</t>
   </si>
 </sst>
 </file>
@@ -7902,8 +7905,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}" name="Table1" displayName="Table1" ref="A1:G953" totalsRowShown="0">
-  <autoFilter ref="A1:G952" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}" name="Table1" displayName="Table1" ref="A1:G955" totalsRowShown="0">
+  <autoFilter ref="A1:G953" xr:uid="{43428C69-B5D7-486D-BCF0-3E3383702390}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G835">
     <sortCondition ref="D2:D835"/>
   </sortState>
@@ -8237,7 +8240,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{207B3246-3E1F-4883-B5B7-F0312ED8EA41}">
-  <dimension ref="A1:G953"/>
+  <dimension ref="A1:G955"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="8.140625" customWidth="1"/>
@@ -19219,6 +19222,28 @@
       </c>
       <c r="D953" s="0" t="s">
         <v>1162</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="B954" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C954" s="0" t="s">
+        <v>2432</v>
+      </c>
+      <c r="D954" s="0" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="B955" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C955" s="0" t="s">
+        <v>2432</v>
+      </c>
+      <c r="D955" s="0" t="s">
+        <v>231</v>
       </c>
     </row>
   </sheetData>
